--- a/structural/h2_delay/data/h2_delay.xlsx
+++ b/structural/h2_delay/data/h2_delay.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="9">
   <si>
     <t>EF</t>
   </si>
@@ -47,16 +47,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -72,7 +64,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -80,30 +72,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,19 +376,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
     </row>
@@ -428,11 +402,11 @@
       <c r="C2">
         <v>2030</v>
       </c>
-      <c r="D2">
-        <v>567.73</v>
-      </c>
-      <c r="E2">
-        <v>21.56</v>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -497,10 +471,10 @@
         <v>2030</v>
       </c>
       <c r="D6">
-        <v>544.58</v>
+        <v>505.6</v>
       </c>
       <c r="E6">
-        <v>34.43</v>
+        <v>43.05</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -513,11 +487,11 @@
       <c r="C7">
         <v>2035</v>
       </c>
-      <c r="D7">
-        <v>566.6900000000001</v>
-      </c>
-      <c r="E7">
-        <v>27.94</v>
+      <c r="D7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -565,10 +539,10 @@
         <v>2030</v>
       </c>
       <c r="D10">
-        <v>541.83</v>
+        <v>502.59</v>
       </c>
       <c r="E10">
-        <v>35.84</v>
+        <v>47.37</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -581,11 +555,11 @@
       <c r="C11">
         <v>2035</v>
       </c>
-      <c r="D11">
-        <v>548.26</v>
-      </c>
-      <c r="E11">
-        <v>37.4</v>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -633,10 +607,10 @@
         <v>2030</v>
       </c>
       <c r="D14">
-        <v>530.12</v>
+        <v>485.7</v>
       </c>
       <c r="E14">
-        <v>19.04</v>
+        <v>20.85</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -649,11 +623,11 @@
       <c r="C15">
         <v>2035</v>
       </c>
-      <c r="D15">
-        <v>537.03</v>
-      </c>
-      <c r="E15">
-        <v>14.15</v>
+      <c r="D15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -666,11 +640,11 @@
       <c r="C16">
         <v>2040</v>
       </c>
-      <c r="D16">
-        <v>548.08</v>
-      </c>
-      <c r="E16">
-        <v>8.01</v>
+      <c r="D16" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -683,11 +657,11 @@
       <c r="C17">
         <v>2045</v>
       </c>
-      <c r="D17">
-        <v>555.58</v>
-      </c>
-      <c r="E17">
-        <v>3.12</v>
+      <c r="D17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -701,10 +675,10 @@
         <v>2030</v>
       </c>
       <c r="D18">
-        <v>524.3099999999999</v>
+        <v>483.36</v>
       </c>
       <c r="E18">
-        <v>28.66</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -718,10 +692,10 @@
         <v>2035</v>
       </c>
       <c r="D19">
-        <v>527.34</v>
+        <v>483.71</v>
       </c>
       <c r="E19">
-        <v>25.79</v>
+        <v>31.52</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -734,11 +708,11 @@
       <c r="C20">
         <v>2040</v>
       </c>
-      <c r="D20">
-        <v>541.59</v>
-      </c>
-      <c r="E20">
-        <v>16.01</v>
+      <c r="D20" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -751,11 +725,11 @@
       <c r="C21">
         <v>2045</v>
       </c>
-      <c r="D21">
-        <v>554.38</v>
-      </c>
-      <c r="E21">
-        <v>3.97</v>
+      <c r="D21" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -769,10 +743,10 @@
         <v>2030</v>
       </c>
       <c r="D22">
-        <v>523.04</v>
+        <v>482.57</v>
       </c>
       <c r="E22">
-        <v>29.3</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -786,10 +760,10 @@
         <v>2035</v>
       </c>
       <c r="D23">
-        <v>523.3200000000001</v>
+        <v>482.57</v>
       </c>
       <c r="E23">
-        <v>30.51</v>
+        <v>38.86</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -802,11 +776,11 @@
       <c r="C24">
         <v>2040</v>
       </c>
-      <c r="D24">
-        <v>537.02</v>
-      </c>
-      <c r="E24">
-        <v>22.76</v>
+      <c r="D24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -819,11 +793,11 @@
       <c r="C25">
         <v>2045</v>
       </c>
-      <c r="D25">
-        <v>553.29</v>
-      </c>
-      <c r="E25">
-        <v>5.96</v>
+      <c r="D25" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -837,10 +811,10 @@
         <v>2030</v>
       </c>
       <c r="D26">
-        <v>509.96</v>
+        <v>466.19</v>
       </c>
       <c r="E26">
-        <v>14.94</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -854,10 +828,10 @@
         <v>2035</v>
       </c>
       <c r="D27">
-        <v>511.77</v>
+        <v>466.19</v>
       </c>
       <c r="E27">
-        <v>12.89</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -871,10 +845,10 @@
         <v>2040</v>
       </c>
       <c r="D28">
-        <v>515.52</v>
+        <v>466.22</v>
       </c>
       <c r="E28">
-        <v>6.75</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -888,10 +862,10 @@
         <v>2045</v>
       </c>
       <c r="D29">
-        <v>517.59</v>
+        <v>466.57</v>
       </c>
       <c r="E29">
-        <v>1.14</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -905,10 +879,10 @@
         <v>2030</v>
       </c>
       <c r="D30">
-        <v>508.41</v>
+        <v>465.96</v>
       </c>
       <c r="E30">
-        <v>18.52</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -922,10 +896,10 @@
         <v>2035</v>
       </c>
       <c r="D31">
-        <v>508.53</v>
+        <v>465.96</v>
       </c>
       <c r="E31">
-        <v>17.93</v>
+        <v>18.33</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -939,10 +913,10 @@
         <v>2040</v>
       </c>
       <c r="D32">
-        <v>513.71</v>
+        <v>465.96</v>
       </c>
       <c r="E32">
-        <v>12.87</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -956,10 +930,10 @@
         <v>2045</v>
       </c>
       <c r="D33">
-        <v>517.37</v>
+        <v>466.38</v>
       </c>
       <c r="E33">
-        <v>2.29</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -973,10 +947,10 @@
         <v>2030</v>
       </c>
       <c r="D34">
-        <v>508.13</v>
+        <v>465.87</v>
       </c>
       <c r="E34">
-        <v>19.36</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -990,10 +964,10 @@
         <v>2035</v>
       </c>
       <c r="D35">
-        <v>508.14</v>
+        <v>465.87</v>
       </c>
       <c r="E35">
-        <v>19.33</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -1007,10 +981,10 @@
         <v>2040</v>
       </c>
       <c r="D36">
-        <v>512.0700000000001</v>
+        <v>465.87</v>
       </c>
       <c r="E36">
-        <v>18.36</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -1024,10 +998,10 @@
         <v>2045</v>
       </c>
       <c r="D37">
-        <v>517.16</v>
+        <v>466.23</v>
       </c>
       <c r="E37">
-        <v>3.43</v>
+        <v>12.41</v>
       </c>
     </row>
   </sheetData>

--- a/structural/h2_delay/data/h2_delay.xlsx
+++ b/structural/h2_delay/data/h2_delay.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="9">
   <si>
     <t>EF</t>
   </si>
@@ -470,11 +470,11 @@
       <c r="C6">
         <v>2030</v>
       </c>
-      <c r="D6">
-        <v>505.6</v>
-      </c>
-      <c r="E6">
-        <v>43.05</v>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -538,11 +538,11 @@
       <c r="C10">
         <v>2030</v>
       </c>
-      <c r="D10">
-        <v>502.59</v>
-      </c>
-      <c r="E10">
-        <v>47.37</v>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -606,11 +606,11 @@
       <c r="C14">
         <v>2030</v>
       </c>
-      <c r="D14">
-        <v>485.7</v>
-      </c>
-      <c r="E14">
-        <v>20.85</v>
+      <c r="D14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -675,10 +675,10 @@
         <v>2030</v>
       </c>
       <c r="D18">
-        <v>483.36</v>
+        <v>491.24</v>
       </c>
       <c r="E18">
-        <v>33.15</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -691,11 +691,11 @@
       <c r="C19">
         <v>2035</v>
       </c>
-      <c r="D19">
-        <v>483.71</v>
-      </c>
-      <c r="E19">
-        <v>31.52</v>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -743,10 +743,10 @@
         <v>2030</v>
       </c>
       <c r="D22">
-        <v>482.57</v>
+        <v>487.93</v>
       </c>
       <c r="E22">
-        <v>38.86</v>
+        <v>30.72</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -759,11 +759,11 @@
       <c r="C23">
         <v>2035</v>
       </c>
-      <c r="D23">
-        <v>482.57</v>
-      </c>
-      <c r="E23">
-        <v>38.86</v>
+      <c r="D23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -811,10 +811,10 @@
         <v>2030</v>
       </c>
       <c r="D26">
-        <v>466.19</v>
+        <v>469.19</v>
       </c>
       <c r="E26">
-        <v>10.72</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -828,10 +828,10 @@
         <v>2035</v>
       </c>
       <c r="D27">
-        <v>466.19</v>
+        <v>469.24</v>
       </c>
       <c r="E27">
-        <v>10.72</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -845,10 +845,10 @@
         <v>2040</v>
       </c>
       <c r="D28">
-        <v>466.22</v>
+        <v>470.79</v>
       </c>
       <c r="E28">
-        <v>9.56</v>
+        <v>4.97</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -862,10 +862,10 @@
         <v>2045</v>
       </c>
       <c r="D29">
-        <v>466.57</v>
+        <v>472.41</v>
       </c>
       <c r="E29">
-        <v>4.14</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -879,10 +879,10 @@
         <v>2030</v>
       </c>
       <c r="D30">
-        <v>465.96</v>
+        <v>468.65</v>
       </c>
       <c r="E30">
-        <v>18.33</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -896,10 +896,10 @@
         <v>2035</v>
       </c>
       <c r="D31">
-        <v>465.96</v>
+        <v>468.65</v>
       </c>
       <c r="E31">
-        <v>18.33</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -913,10 +913,10 @@
         <v>2040</v>
       </c>
       <c r="D32">
-        <v>465.96</v>
+        <v>469.27</v>
       </c>
       <c r="E32">
-        <v>17.98</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -930,10 +930,10 @@
         <v>2045</v>
       </c>
       <c r="D33">
-        <v>466.38</v>
+        <v>471.96</v>
       </c>
       <c r="E33">
-        <v>8.279999999999999</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -947,10 +947,10 @@
         <v>2030</v>
       </c>
       <c r="D34">
-        <v>465.87</v>
+        <v>468.35</v>
       </c>
       <c r="E34">
-        <v>20.07</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -964,10 +964,10 @@
         <v>2035</v>
       </c>
       <c r="D35">
-        <v>465.87</v>
+        <v>468.35</v>
       </c>
       <c r="E35">
-        <v>20.07</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -981,10 +981,10 @@
         <v>2040</v>
       </c>
       <c r="D36">
-        <v>465.87</v>
+        <v>468.61</v>
       </c>
       <c r="E36">
-        <v>20.07</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -998,10 +998,10 @@
         <v>2045</v>
       </c>
       <c r="D37">
-        <v>466.23</v>
+        <v>471.51</v>
       </c>
       <c r="E37">
-        <v>12.41</v>
+        <v>6.21</v>
       </c>
     </row>
   </sheetData>
